--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.30999215556604</v>
+        <v>6.225373725279482</v>
       </c>
       <c r="D2" t="n">
-        <v>39.35738955747351</v>
+        <v>6.395575803089446</v>
       </c>
       <c r="E2" t="n">
-        <v>10.25170446797956</v>
+        <v>1.665901976046679</v>
       </c>
       <c r="F2" t="n">
-        <v>16.66605870947103</v>
+        <v>2.708234540289043</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.11512219615547</v>
+        <v>2.618707356875264</v>
       </c>
       <c r="D3" t="n">
-        <v>1.526266574181978</v>
+        <v>0.2480183183045714</v>
       </c>
       <c r="E3" t="n">
-        <v>10.25170446797956</v>
+        <v>1.665901976046679</v>
       </c>
       <c r="F3" t="n">
-        <v>16.66605870947103</v>
+        <v>2.708234540289043</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.38503528388367</v>
+        <v>6.075068233631096</v>
       </c>
       <c r="D4" t="n">
-        <v>33.72766294554878</v>
+        <v>5.480745228651677</v>
       </c>
       <c r="E4" t="n">
-        <v>10.25170446797956</v>
+        <v>1.665901976046679</v>
       </c>
       <c r="F4" t="n">
-        <v>16.66605870947103</v>
+        <v>2.708234540289043</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
